--- a/branches/cpg-antimicrobiology/ValueSet-condition-valueset.xlsx
+++ b/branches/cpg-antimicrobiology/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T23:12:19+00:00</t>
+    <t>2025-01-05T07:31:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-antimicrobiology/ValueSet-condition-valueset.xlsx
+++ b/branches/cpg-antimicrobiology/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-05T07:31:05+00:00</t>
+    <t>2025-01-10T09:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
